--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2564699</v>
+        <v>110947673</v>
       </c>
       <c r="B2" t="n">
-        <v>105123</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220103</v>
+        <v>100088</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hammaren, 250 m O om, Srm</t>
+          <t>Slängen, strax SV om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624669.7951666209</v>
+        <v>624865</v>
       </c>
       <c r="R2" t="n">
-        <v>6543626.761707954</v>
+        <v>6543383</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>lövskog = fd hagmark</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,53 +777,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2598795</v>
+        <v>124512088</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>102952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hammaren, 250 m O om, Srm</t>
+          <t>Slängen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624669.7951666209</v>
+        <v>624803</v>
       </c>
       <c r="R3" t="n">
-        <v>6543626.761707954</v>
+        <v>6543477</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +861,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>lövskog = fd hagmark</t>
+          <t>kulturlandskap</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,53 +879,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3393313</v>
+        <v>124512085</v>
       </c>
       <c r="B4" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>102963</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hammaren, 250 m O om, Srm</t>
+          <t>Slängen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624669.7951666209</v>
+        <v>624803</v>
       </c>
       <c r="R4" t="n">
-        <v>6543626.761707954</v>
+        <v>6543477</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +963,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>lövskog = fd hagmark</t>
+          <t>kulturlandskap</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1035,53 +981,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3520463</v>
+        <v>110947697</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hammaren, 250 m O om, Srm</t>
+          <t>Slängen, strax SV om, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624669.7951666209</v>
+        <v>624865</v>
       </c>
       <c r="R5" t="n">
-        <v>6543626.761707954</v>
+        <v>6543383</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1065,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>lövskog = fd hagmark</t>
+          <t>åkerkant</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1152,49 +1083,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6353495</v>
+        <v>124512086</v>
       </c>
       <c r="B6" t="n">
-        <v>98932</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224932</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig backsmörblomma</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hammaren, 200 m OSO om, Srm</t>
+          <t>Slängen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624682.5890345083</v>
+        <v>624803</v>
       </c>
       <c r="R6" t="n">
-        <v>6543534.929696078</v>
+        <v>6543477</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,22 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,7 +1167,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>lövskog = fd hagmark</t>
+          <t>kulturlandskap</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2564701</v>
+        <v>132482345</v>
       </c>
       <c r="B7" t="n">
-        <v>105123</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58698</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,46 +1196,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220103</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hammaren 200 m o, Srm</t>
+          <t>Vippala, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624669.7617038598</v>
+        <v>624781</v>
       </c>
       <c r="R7" t="n">
-        <v>6543627.791309938</v>
+        <v>6543251</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,29 +1248,14 @@
           <t>Björnlunda</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>D-Gne-0123</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,77 +1267,77 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Triviallövskog</t>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>lövbacke</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>D-län Floraväktarna</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>D-län Floraväktarna, Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110947673</v>
+        <v>2564699</v>
       </c>
       <c r="B8" t="n">
-        <v>57143</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100088</v>
+        <v>220103</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slängen, strax SV om, Srm</t>
+          <t>Hammaren, 250 m O om, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624864.6297515694</v>
+        <v>624670</v>
       </c>
       <c r="R8" t="n">
-        <v>6543382.63263587</v>
+        <v>6543627</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,22 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-06-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-06-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,7 +1380,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>vägkant</t>
+          <t>lövskog = fd hagmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1517,50 +1398,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115554546</v>
+        <v>2564701</v>
       </c>
       <c r="B9" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220103</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vippala, Srm</t>
+          <t>Hammaren 200 m o, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624830</v>
+        <v>624670</v>
       </c>
       <c r="R9" t="n">
-        <v>6543405</v>
+        <v>6543628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1585,14 +1470,19 @@
           <t>Björnlunda</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D-Gne-0123</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2012-06-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2012-06-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,23 +1494,936 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>triviallövskog</t>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Triviallövskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>D-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>D-län Floraväktarna, Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2598795</v>
+      </c>
+      <c r="B10" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hammaren, 250 m O om, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>624670</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6543627</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2012-06-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2012-06-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>lövskog = fd hagmark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3520463</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hammaren, 250 m O om, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>624670</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6543627</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2012-06-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2012-06-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>lövskog = fd hagmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6866409</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hammaren vid torpet, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>624419</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6543554</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2013-07-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2013-07-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>kvarstående från odling</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3393313</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hammaren, 250 m O om, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>624670</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6543627</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2012-06-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2012-06-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>lövskog = fd hagmark</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6866407</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hammaren vid torpet, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>624419</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6543554</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2013-07-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2013-07-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4434043</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hammaren, 200 m OSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>624683</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6543535</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2012-06-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2012-06-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>lövskog = fd hagmark</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115554546</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vippala, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>624830</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6543405</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>triviallövskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132482366</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vippala, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>624781</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6543251</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>lövbacke</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6353495</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101746</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>224932</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vanlig backsmörblomma</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hammaren, 200 m OSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>624683</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6543535</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2012-06-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2012-06-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>lövskog = fd hagmark</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110947673</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124512088</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124512085</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110947697</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124512086</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132482345</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2564699</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2564701</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2598795</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3520463</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1821,6 +1876,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6866409</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1923,6 +1983,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3393313</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2020,6 +2085,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6866407</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2122,6 +2192,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4434043</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2224,6 +2299,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115554546</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2326,6 +2406,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132482366</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2424,8 +2509,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6353495</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1991,45 +1991,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6866407</v>
+        <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>102419</v>
+        <v>106470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221317</v>
+        <v>221157</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hammaren vid torpet, Srm</t>
+          <t>Vippala, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624419</v>
+        <v>624758</v>
       </c>
       <c r="R14" t="n">
-        <v>6543554</v>
+        <v>6543247</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2056,12 +2056,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2013-07-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2013-07-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2072,6 +2072,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>lövbacke</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2087,16 +2092,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6866407</t>
+          <t>https://artportalen.se/Sighting/136242289</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4434043</v>
+        <v>6866407</v>
       </c>
       <c r="B15" t="n">
-        <v>102560</v>
+        <v>102419</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2104,37 +2109,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222133</v>
+        <v>221317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hammaren, 200 m OSO om, Srm</t>
+          <t>Hammaren vid torpet, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624683</v>
+        <v>624419</v>
       </c>
       <c r="R15" t="n">
-        <v>6543535</v>
+        <v>6543554</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2158,12 +2163,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
+          <t>2013-07-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
+          <t>2013-07-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2174,11 +2179,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>lövskog = fd hagmark</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2194,16 +2194,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4434043</t>
+          <t>https://artportalen.se/Sighting/6866407</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115554546</v>
+        <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>101326</v>
+        <v>107810</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221705</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Melampyrum pratense</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,13 +2235,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624830</v>
+        <v>624758</v>
       </c>
       <c r="R16" t="n">
-        <v>6543405</v>
+        <v>6543247</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>triviallövskog</t>
+          <t>lövbacke</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2301,33 +2301,33 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115554546</t>
+          <t>https://artportalen.se/Sighting/136242227</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132482366</v>
+        <v>4434043</v>
       </c>
       <c r="B17" t="n">
-        <v>101324</v>
+        <v>102560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222782</v>
+        <v>222133</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2338,17 +2338,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vippala, Srm</t>
+          <t>Hammaren, 200 m OSO om, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624781</v>
+        <v>624683</v>
       </c>
       <c r="R17" t="n">
-        <v>6543251</v>
+        <v>6543535</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2012-06-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2012-06-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>lövbacke</t>
+          <t>lövskog = fd hagmark</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2408,50 +2408,54 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132482366</t>
+          <t>https://artportalen.se/Sighting/4434043</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6353495</v>
+        <v>115554546</v>
       </c>
       <c r="B18" t="n">
-        <v>101746</v>
+        <v>101326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>224932</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vanlig backsmörblomma</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hammaren, 200 m OSO om, Srm</t>
+          <t>Vippala, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624683</v>
+        <v>624830</v>
       </c>
       <c r="R18" t="n">
-        <v>6543535</v>
+        <v>6543405</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2475,12 +2479,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2498,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>lövskog = fd hagmark</t>
+          <t>triviallövskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2511,7 +2515,320 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/115554546</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132482366</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vippala, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>624781</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6543251</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>lövbacke</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132482366</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6353495</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101746</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>224932</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vanlig backsmörblomma</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hammaren, 200 m OSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>624683</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6543535</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2012-06-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2012-06-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>lövskog = fd hagmark</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/6353495</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136242236</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104016</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>225103</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vanlig sälg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vippala, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>624758</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6543247</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>lövbacke</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136242236</t>
         </is>
       </c>
     </row>
@@ -2534,6 +2851,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -1994,7 +1994,7 @@
         <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>106470</v>
+        <v>106471</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>107810</v>
+        <v>107811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136242236</v>
       </c>
       <c r="B21" t="n">
-        <v>104016</v>
+        <v>104017</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -1994,7 +1994,7 @@
         <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>106471</v>
+        <v>106477</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>107811</v>
+        <v>107817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136242236</v>
       </c>
       <c r="B21" t="n">
-        <v>104017</v>
+        <v>104023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -1994,7 +1994,7 @@
         <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>106477</v>
+        <v>106478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>107817</v>
+        <v>107818</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136242236</v>
       </c>
       <c r="B21" t="n">
-        <v>104023</v>
+        <v>104024</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -1994,7 +1994,7 @@
         <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>106478</v>
+        <v>106489</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>107818</v>
+        <v>107829</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136242236</v>
       </c>
       <c r="B21" t="n">
-        <v>104024</v>
+        <v>104035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -1994,7 +1994,7 @@
         <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>106489</v>
+        <v>106502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>107829</v>
+        <v>107842</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136242236</v>
       </c>
       <c r="B21" t="n">
-        <v>104035</v>
+        <v>104048</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -1994,7 +1994,7 @@
         <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>107842</v>
+        <v>107843</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136242236</v>
       </c>
       <c r="B21" t="n">
-        <v>104048</v>
+        <v>104049</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -1994,7 +1994,7 @@
         <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>106503</v>
+        <v>106516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>107843</v>
+        <v>107856</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136242236</v>
       </c>
       <c r="B21" t="n">
-        <v>104049</v>
+        <v>104062</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -1994,7 +1994,7 @@
         <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>106516</v>
+        <v>106517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>107856</v>
+        <v>107857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136242236</v>
       </c>
       <c r="B21" t="n">
-        <v>104062</v>
+        <v>104063</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
